--- a/基金/持仓基金/006663_易方达安悦超短债C/006663_交易记录.xlsx
+++ b/基金/持仓基金/006663_易方达安悦超短债C/006663_交易记录.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\Documents\AI 投研\基金\006663_易方达安悦超短债C\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\Documents\AI 投研\基金\持仓基金\006663_易方达安悦超短债C\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="15825" windowHeight="12165"/>
+    <workbookView windowWidth="16065" windowHeight="12750"/>
   </bookViews>
   <sheets>
     <sheet name="交易记录" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="8">
   <si>
     <t>交易日期</t>
   </si>
@@ -704,7 +704,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -724,6 +724,7 @@
     <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="31" fontId="0" fillId="0" borderId="0" xfId="49" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="49" applyFont="1"/>
   </cellXfs>
   <cellStyles count="50">
@@ -1002,7 +1003,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Transactions_006663" displayName="Transactions_006663" ref="A1:F7" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Transactions_006663" displayName="Transactions_006663" ref="A1:F8" totalsRowShown="0">
   <tableColumns count="6">
     <tableColumn id="1" name="交易日期"/>
     <tableColumn id="2" name="成交净值"/>
@@ -1212,8 +1213,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="6" outlineLevelCol="5"/>
+  <dimension ref="A1:F8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="7" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="2" width="18" customWidth="1"/>
     <col min="3" max="3" width="21" customWidth="1"/>
@@ -1348,17 +1349,44 @@
       </c>
     </row>
     <row r="7" spans="1:6">
+      <c r="A7" s="7">
+        <v>46315</v>
+      </c>
+      <c r="B7">
+        <v>1.0128</v>
+      </c>
       <c r="C7">
         <v>5000</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="D7" s="8" t="s">
         <v>7</v>
+      </c>
+      <c r="E7">
+        <v>5064</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="7">
+        <v>46316</v>
+      </c>
+      <c r="C8" t="e">
+        <f>E8/B8</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E8">
+        <v>20000</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" sqref="D7 D2:D6">
-      <formula1>"买入,卖出"</formula1>
+    <dataValidation type="list" sqref="D2:D8">
+      <formula1>"买入,卖出,转入"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
